--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N81_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.57502869929871</v>
+        <v>10.16844216363604</v>
       </c>
       <c r="D2" t="n">
-        <v>51.95428833437312</v>
+        <v>8.442571854335633</v>
       </c>
       <c r="E2" t="n">
-        <v>18.53477348871925</v>
+        <v>3.011900691916878</v>
       </c>
       <c r="F2" t="n">
-        <v>14.95041580031916</v>
+        <v>2.429442567551863</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.96516787953581</v>
+        <v>3.244339780424569</v>
       </c>
       <c r="D3" t="n">
-        <v>16.44726840537679</v>
+        <v>2.672681115873728</v>
       </c>
       <c r="E3" t="n">
-        <v>18.53477348871925</v>
+        <v>3.011900691916878</v>
       </c>
       <c r="F3" t="n">
-        <v>14.95041580031916</v>
+        <v>2.429442567551863</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.31753289268895</v>
+        <v>10.28909909506195</v>
       </c>
       <c r="D4" t="n">
-        <v>36.94185945784584</v>
+        <v>6.00305216189995</v>
       </c>
       <c r="E4" t="n">
-        <v>18.53477348871925</v>
+        <v>3.011900691916878</v>
       </c>
       <c r="F4" t="n">
-        <v>14.95041580031916</v>
+        <v>2.429442567551863</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.39320951157135</v>
+        <v>10.13889654563035</v>
       </c>
       <c r="D5" t="n">
-        <v>53.68600875583269</v>
+        <v>8.723976422822812</v>
       </c>
       <c r="E5" t="n">
-        <v>18.53477348871925</v>
+        <v>3.011900691916878</v>
       </c>
       <c r="F5" t="n">
-        <v>14.95041580031916</v>
+        <v>2.429442567551863</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
